--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -324,17 +324,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:GOQASy66</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -344,52 +344,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>home</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>16.93</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -419,24 +419,24 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>Match status live; not yet settled.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -451,37 +451,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0573</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -520,108 +520,6 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>Match status live; not yet settled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:12 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
         <is>
           <t>Match status live; not yet settled.</t>
         </is>
@@ -957,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1059,7 +957,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1059,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1402,7 +1300,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1336,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1420,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -160,7 +160,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -160,7 +160,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:n1pZG14F</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,52 +140,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -215,24 +215,24 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Match status live; not yet settled.</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:2qevfSqS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -242,17 +242,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,62 +855,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -957,17 +957,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -982,37 +982,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0573</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1051,108 +1051,6 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>Match status live; not yet settled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 07:34:23 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>Match status live; not yet settled.</t>
         </is>
@@ -1300,7 +1198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1282,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1318,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,12 +120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -135,57 +135,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t/>
+          <t>home</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>16.93</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -215,79 +215,79 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>Match status live; not yet settled.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -307,7 +307,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -316,210 +316,6 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Match status live; not yet settled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
         <is>
           <t>Match status live; not yet settled.</t>
         </is>
@@ -855,7 +651,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -957,7 +753,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1198,7 +994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1030,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1114,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-05 16:18:29 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -185,44 +185,44 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>draw</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Match status live; not yet settled.</t>
+          <t>[SofaScore] Pick home missed actual draw. Score 3-3.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-05 16:18:29 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -287,37 +287,37 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>home</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-20.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Match status live; not yet settled.</t>
+          <t>[SofaScore] Pick away missed actual home. Score 1-0.</t>
         </is>
       </c>
     </row>
@@ -539,6 +539,210 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:29 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>flashscore:rTwrFuZR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.2111</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.0573</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-16.93</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>[SofaScore] Pick home missed actual draw. Score 3-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05 16:18:29 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flashscore:zs3PZaZa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.4819</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-20.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[SofaScore] Pick away missed actual home. Score 1-0.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -648,210 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Match status live; not yet settled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Match status live; not yet settled.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -879,7 +879,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36.93</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-36.93</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-05 16:18:29 ACST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>feed_health</t>
+          <t>sofa_health</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1013,55 +1013,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feed_note</t>
+          <t>flashscore_health</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>healthy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>phase5_input_rows</t>
+          <t>flashscore_note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rows_settled_this_run</t>
+          <t>phase5_input_rows</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>won_this_run</t>
+          <t>rows_settled_this_run</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lost_this_run</t>
+          <t>won_this_run</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>lost_this_run</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>void</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,10 +1109,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,204 +120,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 16:18:29 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>16072838</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0573</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[SofaScore] Pick home missed actual draw. Score 3-3.</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 16:18:29 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>16115678</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-20.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[SofaScore] Pick away missed actual home. Score 1-0.</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
@@ -539,210 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 16:18:29 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-16.93</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>[SofaScore] Pick home missed actual draw. Score 3-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 16:18:29 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-20.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[SofaScore] Pick away missed actual home. Score 1-0.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -994,7 +1096,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 16:18:29 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1156,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1180,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1228,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,12 +222,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -237,7 +237,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -247,12 +247,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,12 +324,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -339,7 +339,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -349,12 +349,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,37 +426,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -528,100 +528,508 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -1096,7 +1504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1552,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1636,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,102 +120,6120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17 03:55:53 ACST</t>
+          <t>2026-05-17 13:39:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>flashscore:juAhRoT7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.451</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.3399</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>[SofaScore] Match in progress (1-2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flashscore:GMTLJkHb</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>flashscore:ClNUHToB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chiba</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>flashscore:p2LxG7GN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Okayama</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>flashscore:UPgeYlWi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>flashscore:4n29Aovo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kyoto</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>flashscore:jH1dEhfL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>flashscore:6V6CE1l4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.2592</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.1683</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flashscore:2c0LCuJG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.3004</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0899</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>flashscore:SrG1hBX1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.2921</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.1103</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>flashscore:b5oCU6VG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flashscore:fk8mGEP8</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.2275</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.1164</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flashscore:r7lSurwo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>flashscore:h8KKYP3b</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.2439</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.0621</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>flashscore:6Ho2GrlU</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Telstar</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flashscore:lIKARQtP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.0578</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>flashscore:p2cgI4JH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>flashscore:hfunKQl5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>G.A. Eagles</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>flashscore:OEmVN8kt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.5283</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.0521</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>flashscore:21M2TnCC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.5939</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.2606</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>flashscore:dtRBznZo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sittard</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.294</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.1273</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>flashscore:dSowMnKh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>flashscore:6TRhfX2k</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.2101</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.0672</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flashscore:MF2Xj8on</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.2914</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.0914</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>flashscore:jeflmQpB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.2886</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0.0577</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>flashscore:OM7eo4FN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.3893</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0.0863</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>flashscore:dIYdxCy9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>flashscore:bX3pLsxi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>MLS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>CF Montreal</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Chicago Fire</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>flashscore:21IEQ3ET</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>flashscore:6PmDxLVi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>flashscore:SvxMza04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>flashscore:EezUYxVG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>flashscore:8dh2GUEk</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>flashscore:tAjAE8q2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>flashscore:nmDyVTTr</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>flashscore:fDGqT7be</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>San Diego FC</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>flashscore:2Fy5zj6L</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>flashscore:I9QHhKRp</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>flashscore:vyaxjXte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>flashscore:n12plBB7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>flashscore:0OhvAhYQ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>flashscore:K8ZA4Wel</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>flashscore:YFVo6qXh</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.3284</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0.0975</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>flashscore:C0sw852t</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>flashscore:hMXI2AQ0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>no_value</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=no_value).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>flashscore:llRR0leD</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.3524</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>flashscore:ttZg4N15</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.3552</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.0522</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>flashscore:YH84GNJi</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.3733</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0792</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>flashscore:nmmS8WHr</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.4881</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.1064</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>flashscore:h0IS6Ane</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.6295</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.2128</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>flashscore:prPnPy9r</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>flashscore:IXv8WJG8</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.2297</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0.1047</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>flashscore:r1cGQTSk</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.5144</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0.1327</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>flashscore:OhrGQlpm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.6381</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0.0499</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>flashscore:xbwdLg87</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>flashscore:z9FNO7c2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.4328</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0.0406</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>flashscore:QcrGUcoL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.1691</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0.0638</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>flashscore:IeNfNFwe</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>flashscore:44Vsqc0E</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.5144</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0.1918</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>flashscore:SduXBE3E</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.2879</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0.1703</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
@@ -546,6 +6564,2760 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>flashscore:juAhRoT7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.451</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.3399</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>[SofaScore] Match in progress (1-2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flashscore:6V6CE1l4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.2592</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.1683</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>flashscore:2c0LCuJG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.3004</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.0899</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>flashscore:SrG1hBX1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.2921</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.1103</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>flashscore:fk8mGEP8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.2275</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.1164</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>flashscore:h8KKYP3b</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.2439</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0621</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>flashscore:lIKARQtP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0578</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>flashscore:OEmVN8kt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.5283</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0521</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flashscore:21M2TnCC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.5939</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.2606</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>flashscore:dtRBznZo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sittard</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.294</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.1273</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>flashscore:6TRhfX2k</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.2101</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0672</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flashscore:MF2Xj8on</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.2914</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0914</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flashscore:jeflmQpB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.2886</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0577</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>flashscore:OM7eo4FN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.3893</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.0863</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>flashscore:YFVo6qXh</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.3284</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.0975</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flashscore:llRR0leD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.3524</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.0494</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>flashscore:ttZg4N15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.3552</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0522</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>flashscore:YH84GNJi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.3733</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.0792</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>flashscore:nmmS8WHr</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.4881</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.1064</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>flashscore:h0IS6Ane</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.6295</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.2128</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>flashscore:IXv8WJG8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.2297</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.1047</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>flashscore:r1cGQTSk</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.5144</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.1327</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>flashscore:OhrGQlpm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.6381</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.0499</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flashscore:z9FNO7c2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.4328</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.0406</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>flashscore:QcrGUcoL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.1691</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0.0638</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lean</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>flashscore:44Vsqc0E</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.5144</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0.1918</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-17 13:39:47 ACST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>flashscore:SduXBE3E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.2879</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.1703</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>[Flashscore] Match in progress (None-None).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -688,7 +9460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-17 03:55:53 ACST</t>
+          <t>2026-05-17 13:39:47 ACST</t>
         </is>
       </c>
     </row>
@@ -736,7 +9508,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -784,7 +9556,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -820,7 +9592,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:juAhRoT7</t>
+          <t>flashscore:ClNUHToB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,62 +140,62 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Chiba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -205,7 +205,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -215,19 +215,19 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[SofaScore] Match in progress (1-2).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:GMTLJkHb</t>
+          <t>flashscore:p2LxG7GN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -242,17 +242,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Okayama</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,12 +324,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:ClNUHToB</t>
+          <t>flashscore:UPgeYlWi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -344,17 +344,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chiba</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,12 +426,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:p2LxG7GN</t>
+          <t>flashscore:4n29Aovo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Okayama</t>
+          <t>Kyoto</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -528,17 +528,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flashscore:UPgeYlWi</t>
+          <t>flashscore:jH1dEhfL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -623,24 +623,24 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flashscore:4n29Aovo</t>
+          <t>flashscore:6V6CE1l4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -650,52 +650,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kyoto</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t/>
+          <t>11.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t/>
+          <t>0.19355830508474575</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -725,19 +725,19 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flashscore:jH1dEhfL</t>
+          <t>flashscore:2c0LCuJG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,32 +757,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>home</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2571843012364181</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0572</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>no_value</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>flashscore:6V6CE1l4</t>
+          <t>flashscore:SrG1hBX1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,42 +859,42 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.2592</t>
+          <t>0.2464353880927423</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.0646</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -936,17 +936,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flashscore:2c0LCuJG</t>
+          <t>flashscore:b5oCU6VG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -961,47 +961,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Machida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t/>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t/>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0899</t>
+          <t/>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t/>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1031,19 +1031,19 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flashscore:SrG1hBX1</t>
+          <t>flashscore:fk8mGEP8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1063,42 +1063,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.2921</t>
+          <t>0.18378077821011674</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.1103</t>
+          <t>0.0727</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1140,17 +1140,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flashscore:b5oCU6VG</t>
+          <t>flashscore:r7lSurwo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1242,17 +1242,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flashscore:fk8mGEP8</t>
+          <t>flashscore:h8KKYP3b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1262,52 +1262,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.2275</t>
+          <t/>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t/>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1337,24 +1337,24 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flashscore:r7lSurwo</t>
+          <t>flashscore:6Ho2GrlU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1439,19 +1439,19 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flashscore:h8KKYP3b</t>
+          <t>flashscore:lIKARQtP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t/>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.2439</t>
+          <t/>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0621</t>
+          <t/>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>flashscore:6Ho2GrlU</t>
+          <t>flashscore:p2cgI4JH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1650,12 +1650,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>flashscore:lIKARQtP</t>
+          <t>flashscore:hfunKQl5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1675,47 +1675,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Nijmegen</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>G.A. Eagles</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t/>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.0578</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1745,19 +1745,19 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>flashscore:p2cgI4JH</t>
+          <t>flashscore:OEmVN8kt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,12 +1854,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>flashscore:hfunKQl5</t>
+          <t>flashscore:21M2TnCC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1879,47 +1879,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nijmegen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>G.A. Eagles</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t/>
+          <t>0.46492481856603696</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1949,19 +1949,19 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>flashscore:OEmVN8kt</t>
+          <t>flashscore:dtRBznZo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1981,32 +1981,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sittard</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.5283</t>
+          <t>0.24081564655916007</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0521</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2058,12 +2058,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flashscore:21M2TnCC</t>
+          <t>flashscore:dSowMnKh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2083,47 +2083,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Zwolle</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.5939</t>
+          <t/>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.2606</t>
+          <t/>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2153,24 +2153,24 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>flashscore:dtRBznZo</t>
+          <t>flashscore:6TRhfX2k</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2180,52 +2180,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sittard</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t/>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t/>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2255,24 +2255,24 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>flashscore:dSowMnKh</t>
+          <t>flashscore:MF2Xj8on</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2282,37 +2282,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zwolle</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2529180530373343</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0529</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>no_value</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t/>
+          <t>live</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2357,24 +2357,24 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>flashscore:6TRhfX2k</t>
+          <t>flashscore:jeflmQpB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2384,37 +2384,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.2101</t>
+          <t/>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.0672</t>
+          <t/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>flashscore:MF2Xj8on</t>
+          <t>flashscore:OM7eo4FN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2491,47 +2491,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t/>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t/>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.0914</t>
+          <t/>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>flashscore:jeflmQpB</t>
+          <t>flashscore:dIYdxCy9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2588,52 +2588,52 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t/>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.0577</t>
+          <t/>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2663,24 +2663,24 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>flashscore:OM7eo4FN</t>
+          <t>flashscore:bX3pLsxi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2690,52 +2690,52 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>CF Montreal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t/>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.0863</t>
+          <t/>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t/>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2765,19 +2765,19 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>flashscore:dIYdxCy9</t>
+          <t>flashscore:21IEQ3ET</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sporting Kansas City</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2874,12 +2874,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>flashscore:bX3pLsxi</t>
+          <t>flashscore:6PmDxLVi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2976,12 +2976,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>flashscore:21IEQ3ET</t>
+          <t>flashscore:SvxMza04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3078,12 +3078,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>flashscore:6PmDxLVi</t>
+          <t>flashscore:EezUYxVG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York Red Bulls</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3180,12 +3180,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>flashscore:SvxMza04</t>
+          <t>flashscore:8dh2GUEk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlanta Utd</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3282,12 +3282,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>flashscore:EezUYxVG</t>
+          <t>flashscore:tAjAE8q2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New York Red Bulls</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>flashscore:8dh2GUEk</t>
+          <t>flashscore:nmDyVTTr</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Atlanta Utd</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3486,12 +3486,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>flashscore:tAjAE8q2</t>
+          <t>flashscore:fDGqT7be</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3588,12 +3588,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>flashscore:nmDyVTTr</t>
+          <t>flashscore:juAhRoT7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Jose Earthquakes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3690,12 +3690,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>flashscore:fDGqT7be</t>
+          <t>flashscore:2Fy5zj6L</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Diego FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Los Angeles Galaxy</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3792,17 +3792,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>flashscore:2Fy5zj6L</t>
+          <t>flashscore:GMTLJkHb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>J1 League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Los Angeles Galaxy</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3996,7 +3996,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4098,7 +4098,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4200,7 +4200,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4404,7 +4404,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4449,22 +4449,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.2836728987320498</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.0975</t>
+          <t>0.0527</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4506,7 +4506,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4710,7 +4710,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4745,22 +4745,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t/>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.0494</t>
+          <t/>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t/>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t/>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4949,37 +4949,37 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.3733</t>
+          <t/>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.0792</t>
+          <t/>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.4881</t>
+          <t>0.42763439123578717</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5118,7 +5118,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.6295</t>
+          <t>0.5166484711779449</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.2128</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5220,7 +5220,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5322,7 +5322,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5362,27 +5362,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.2297</t>
+          <t>0.19364614172916342</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.1047</t>
+          <t>0.0603</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5469,22 +5469,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.5144</t>
+          <t>0.44293367303609343</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.0613</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5526,7 +5526,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5561,22 +5561,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t/>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.6381</t>
+          <t/>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.0499</t>
+          <t/>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5730,7 +5730,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5765,22 +5765,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t/>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t/>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.0406</t>
+          <t/>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5867,22 +5867,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t/>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.1691</t>
+          <t/>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0.0638</t>
+          <t/>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -5927,14 +5927,14 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=no_value).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6036,7 +6036,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6076,22 +6076,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.5144</t>
+          <t>0.42364591065292095</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.1918</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6138,7 +6138,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.2879</t>
+          <t>0.21563217634709592</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1104</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6567,17 +6567,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:juAhRoT7</t>
+          <t>flashscore:6V6CE1l4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6587,42 +6587,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.19355830508474575</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.1026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -6662,19 +6662,19 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[SofaScore] Match in progress (1-2).</t>
+          <t>[Flashscore] Match in progress (None-None).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:6V6CE1l4</t>
+          <t>flashscore:2c0LCuJG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6694,42 +6694,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.2592</t>
+          <t>0.2571843012364181</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.0572</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6771,12 +6771,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:2c0LCuJG</t>
+          <t>flashscore:SrG1hBX1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6796,42 +6796,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t>0.2464353880927423</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0899</t>
+          <t>0.0646</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -6873,12 +6873,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:SrG1hBX1</t>
+          <t>flashscore:fk8mGEP8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6898,42 +6898,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.2921</t>
+          <t>0.18378077821011674</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1103</t>
+          <t>0.0727</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -6975,17 +6975,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flashscore:fk8mGEP8</t>
+          <t>flashscore:21M2TnCC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6995,42 +6995,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.2275</t>
+          <t>0.46492481856603696</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -7077,12 +7077,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flashscore:h8KKYP3b</t>
+          <t>flashscore:dtRBznZo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7102,32 +7102,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Sittard</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.2439</t>
+          <t>0.24081564655916007</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0621</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -7179,17 +7179,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flashscore:lIKARQtP</t>
+          <t>flashscore:MF2Xj8on</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7199,37 +7199,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.2529180530373343</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0578</t>
+          <t>0.0529</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -7281,57 +7281,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>flashscore:OEmVN8kt</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.5283</t>
+          <t>0.2836728987320498</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0521</t>
+          <t>0.0527</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -7383,67 +7383,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flashscore:21M2TnCC</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.5939</t>
+          <t>0.42763439123578717</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2606</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -7485,62 +7485,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flashscore:dtRBznZo</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sittard</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.5166484711779449</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -7587,57 +7587,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flashscore:6TRhfX2k</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.2101</t>
+          <t>0.19364614172916342</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0672</t>
+          <t>0.0603</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -7689,67 +7689,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flashscore:MF2Xj8on</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.44293367303609343</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0914</t>
+          <t>0.0613</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>lean</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -7791,67 +7791,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flashscore:jeflmQpB</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.42364591065292095</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0577</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lean</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -7893,62 +7893,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flashscore:OM7eo4FN</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.21563217634709592</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0863</t>
+          <t>0.1104</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7987,1332 +7987,6 @@
         </is>
       </c>
       <c r="T15" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>flashscore:YFVo6qXh</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.3284</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.0975</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>flashscore:llRR0leD</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.0494</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>flashscore:ttZg4N15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.3552</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.0522</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>flashscore:YH84GNJi</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.3733</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.0792</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>flashscore:nmmS8WHr</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sassuolo</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0.4881</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.1064</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>flashscore:h0IS6Ane</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0.6295</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.2128</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>flashscore:IXv8WJG8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0.2297</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.1047</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>flashscore:r1cGQTSk</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0.5144</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.1327</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>flashscore:OhrGQlpm</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0.6381</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.0499</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>flashscore:z9FNO7c2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0.4328</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.0406</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>flashscore:QcrGUcoL</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0.1691</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.0638</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.5144</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.1918</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-05-17 13:39:47 ACST</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0.2879</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.1703</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>5.88</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
         <is>
           <t>[Flashscore] Match in progress (None-None).</t>
         </is>
@@ -9460,7 +8134,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-17 13:39:47 ACST</t>
+          <t>2026-05-17 16:16:15 ACST</t>
         </is>
       </c>
     </row>
@@ -9556,7 +8230,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -9592,7 +8266,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:I9QHhKRp</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -175,59 +175,59 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -247,12 +247,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,12 +324,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -349,12 +349,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,12 +426,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -481,59 +481,59 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -583,59 +583,59 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -655,89 +655,89 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t/>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.2856162766780178</t>
+          <t/>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0475</t>
+          <t/>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -834,12 +834,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -889,59 +889,59 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -991,64 +991,64 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1093,59 +1093,59 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1195,59 +1195,59 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1267,94 +1267,94 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t/>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.43150495052825755</t>
+          <t/>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0498</t>
+          <t/>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1364,52 +1364,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t/>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.5228536976696226</t>
+          <t/>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t/>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1439,19 +1439,19 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1548,12 +1548,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1573,89 +1573,89 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t/>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.18495036390101893</t>
+          <t/>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t/>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1675,89 +1675,89 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t/>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.4516464966096222</t>
+          <t/>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.0595</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1807,59 +1807,59 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1956,12 +1956,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2011,59 +2011,59 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2113,59 +2113,59 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>no_value</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>No recommendation (phase5_status=no_value).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2262,17 +2262,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2282,52 +2282,52 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>home</t>
+          <t/>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.4294426966292135</t>
+          <t/>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.0961</t>
+          <t/>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2357,24 +2357,24 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:I9QHhKRp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2384,52 +2384,52 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.22190990936555893</t>
+          <t/>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.0969</t>
+          <t/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>live</t>
+          <t/>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
       </c>
     </row>
@@ -2790,720 +2790,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>flashscore:YFVo6qXh</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.2856162766780178</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0475</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>flashscore:nmmS8WHr</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sassuolo</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.43150495052825755</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.0498</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flashscore:h0IS6Ane</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.5228536976696226</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.1147</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>flashscore:IXv8WJG8</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.18495036390101893</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0673</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>flashscore:r1cGQTSk</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.4516464966096222</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0595</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lean</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.4294426966292135</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0961</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:57:08 ACST</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.22190990936555893</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0969</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>[Flashscore] Match in progress (None-None).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3646,7 +2932,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:57:08 ACST</t>
+          <t>2026-05-18 04:09:11 ACST</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3028,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3064,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,17 +222,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -242,17 +242,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,17 +324,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -344,17 +344,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,17 +426,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -528,17 +528,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -650,17 +650,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -732,17 +732,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -834,17 +834,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -936,17 +936,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,17 +1038,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1140,17 +1140,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1242,17 +1242,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1344,17 +1344,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:I9QHhKRp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1446,17 +1446,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1548,17 +1548,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1650,17 +1650,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1752,17 +1752,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1956,17 +1956,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2058,17 +2058,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2160,17 +2160,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2262,12 +2262,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2364,17 +2364,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>flashscore:I9QHhKRp</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,12 +120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,12 +222,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -247,12 +247,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:27 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:27 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:27 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:27 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:27 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:27 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,37 +120,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:17 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -214,210 +214,6 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -892,7 +688,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:17 ACST</t>
         </is>
       </c>
     </row>
@@ -940,7 +736,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1024,7 +820,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,12 +120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:17 ACST</t>
+          <t>2026-05-19 17:59:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -135,22 +135,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -214,6 +214,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:56 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -688,7 +790,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:17 ACST</t>
+          <t>2026-05-19 17:59:56 ACST</t>
         </is>
       </c>
     </row>
@@ -736,7 +838,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -820,7 +922,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:56 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:56 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:56 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,12 +120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,12 +222,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -242,17 +242,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:09 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,37 +120,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:09 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,37 +222,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:09 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -316,6 +316,414 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -790,7 +1198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:09 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
     </row>
@@ -838,7 +1246,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -922,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,12 +120,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>thesportsdb:2475105</t>
+          <t>16195914</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -145,12 +145,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,37 +222,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>thesportsdb:2475106</t>
+          <t>16197899</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Primeira Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,37 +324,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>thesportsdb:2265408</t>
+          <t>16196423</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AFC Ajax</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,37 +426,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>thesportsdb:2279766</t>
+          <t>16163439</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>VfL Wolfsburg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>SC Paderborn 07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -528,22 +528,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>thesportsdb:2279764</t>
+          <t>16196426</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SC Heerenveen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -630,100 +630,6730 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>thesportsdb:2279765</t>
+          <t>16189758</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Partick Thistle</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15345966</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Urawa Red Diamonds</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13980080</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15345881</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15345880</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16194271</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A-League Men</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Auckland FC</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sydney FC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15345963</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FC Tokyo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15345959</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>JEF United Chiba</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15345871</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga FC</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16172173</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16206585</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13980079</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16195916</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13980072</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15171571</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>St.Louis City</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14083715</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>LaLiga</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14083706</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14083719</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14083723</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14083743</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Girona FC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14083727</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14083710</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Real Betis</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Levante</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14083731</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14083739</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15171576</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15171569</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15171572</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15171573</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Orlando City SC</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>15171574</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15171578</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>New York City FC</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>15171575</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15171577</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>15171581</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>15171580</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>San Diego FC</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15171579</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>15345869</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15345955</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mito Hollyhock</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15345960</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15345868</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16199215</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Stockport County</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16184536</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stockport County</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>13980074</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14023959</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>14023960</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>14023963</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>14023965</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>14023962</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>14023961</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>14023964</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>14023966</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14023967</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>14023968</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>13980061</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SSC Napoli</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>13980070</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>13980064</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>13980066</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>13980071</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>13980077</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>14083735</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>15171588</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>15171584</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15171582</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>16189253</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>League Two</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>16163444</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>16189849</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Partick Thistle</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:57:54 ACST</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>16198895</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -1198,7 +7828,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:58:04 ACST</t>
+          <t>2026-05-20 17:57:54 ACST</t>
         </is>
       </c>
     </row>
@@ -1246,7 +7876,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -1330,7 +7960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>71</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,17 +222,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -247,12 +247,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,12 +324,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -344,17 +344,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,12 +426,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -446,17 +446,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,17 +120,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -140,17 +140,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,17 +222,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -242,17 +242,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,12 +324,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -344,17 +344,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,37 +120,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -214,312 +214,6 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>flashscore:rJKJ2MZP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GAIS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>No recommendation (phase5_status=upstream_blocked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -994,7 +688,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
     </row>
@@ -1042,7 +736,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1126,7 +820,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:20 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:20 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:20 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -140,7 +140,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:20 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,100 +120,304 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:zHabevSa</t>
+          <t>flashscore:fXvLSp0T</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -688,7 +892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
     </row>
@@ -736,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -820,7 +1024,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,7 +120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -222,7 +222,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -324,7 +324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase6_Settlement.xlsx
+++ b/docs/agent-system/outputs/Phase6_Settlement.xlsx
@@ -120,37 +120,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -222,37 +222,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -324,37 +324,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -418,6 +418,1842 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>No recommendation (phase5_status=upstream_blocked).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>No recommendation (phase5_status=upstream_blocked).</t>
         </is>
@@ -892,7 +2728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
     </row>
@@ -940,7 +2776,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1024,7 +2860,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
